--- a/DOSSIES_MULTIFORMATO/SALUX/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SALUX/dossie.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>05.113.942/0001-08</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/SALUX/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SALUX/dossie.xlsx
@@ -577,7 +577,11 @@
           <t>data_prescricao_proxima</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2029-11-30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
